--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.56813747025891</v>
+        <v>5.129822338917074</v>
       </c>
       <c r="D2" t="n">
-        <v>31.04932098172283</v>
+        <v>5.04551465952996</v>
       </c>
       <c r="E2" t="n">
-        <v>10.92648639653192</v>
+        <v>1.775554039436437</v>
       </c>
       <c r="F2" t="n">
-        <v>10.96476096418012</v>
+        <v>1.78177365667927</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.78480567174839</v>
+        <v>5.977530921659114</v>
       </c>
       <c r="D3" t="n">
-        <v>37.59894741307797</v>
+        <v>6.109828954625169</v>
       </c>
       <c r="E3" t="n">
-        <v>10.92648639653192</v>
+        <v>1.775554039436437</v>
       </c>
       <c r="F3" t="n">
-        <v>10.96476096418012</v>
+        <v>1.78177365667927</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.41541069181717</v>
+        <v>2.18000423742029</v>
       </c>
       <c r="D4" t="n">
-        <v>14.41097365266934</v>
+        <v>2.341783218558768</v>
       </c>
       <c r="E4" t="n">
-        <v>10.92648639653192</v>
+        <v>1.775554039436437</v>
       </c>
       <c r="F4" t="n">
-        <v>10.96476096418012</v>
+        <v>1.78177365667927</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.1464140030949</v>
+        <v>2.298792275502922</v>
       </c>
       <c r="D5" t="n">
-        <v>14.17842751416716</v>
+        <v>2.303994471052163</v>
       </c>
       <c r="E5" t="n">
-        <v>10.92648639653192</v>
+        <v>1.775554039436437</v>
       </c>
       <c r="F5" t="n">
-        <v>10.96476096418012</v>
+        <v>1.78177365667927</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>9.526715781904565</v>
+        <v>1.548091314559492</v>
       </c>
       <c r="D6" t="n">
-        <v>9.37305814264149</v>
+        <v>1.523121948179242</v>
       </c>
       <c r="E6" t="n">
-        <v>10.92648639653192</v>
+        <v>1.775554039436437</v>
       </c>
       <c r="F6" t="n">
-        <v>10.96476096418012</v>
+        <v>1.78177365667927</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
